--- a/Excel/AurasAttrConfig.xlsx
+++ b/Excel/AurasAttrConfig.xlsx
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="28">
   <si>
     <t>ID</t>
   </si>
@@ -94,6 +94,9 @@
     <t>int</t>
   </si>
   <si>
+    <t>double</t>
+  </si>
+  <si>
     <t>string</t>
   </si>
   <si>
@@ -139,7 +142,10 @@
     <t>友方减伤倍率增加{0}%</t>
   </si>
   <si>
-    <t>未设定</t>
+    <t>命中光环</t>
+  </si>
+  <si>
+    <t>友方命中概率增加{0}%</t>
   </si>
 </sst>
 </file>
@@ -1218,13 +1224,13 @@
         <v>9</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K5" s="2"/>
     </row>
@@ -1248,10 +1254,10 @@
         <v>1</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -1274,10 +1280,10 @@
         <v>1</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -1300,10 +1306,10 @@
         <v>1</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -1326,10 +1332,10 @@
         <v>3</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -1352,10 +1358,10 @@
         <v>1</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -1378,10 +1384,10 @@
         <v>1</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -1404,10 +1410,10 @@
         <v>1</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="3:10">
@@ -1421,19 +1427,19 @@
         <v>1</v>
       </c>
       <c r="F13" s="1">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G13" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13" s="1">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" customHeight="1"/>
@@ -1446,7 +1452,7 @@
     <row r="21" s="1" customFormat="1" customHeight="1"/>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="D3 E3 F3 G3 D4 E4 F4 G4 D5 E5 F5 C3:C5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="D3:G3 E4:G4 E5:F5 C3:C5 D4:D5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
